--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="487">
   <si>
     <t>Filename</t>
   </si>
@@ -808,679 +808,673 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9935,0.0010,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.0008,0.0002,0.9991</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0674,0.0000,0.0000,0.9924</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0187,0.0003,0.0000,0.9972</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9615,0.0013,0.0306,0.0000</t>
+  </si>
+  <si>
+    <t>0.0107,0.0008,0.9854,0.0017</t>
+  </si>
+  <si>
+    <t>0.0483,0.0054,0.9430,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0011,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0132,0.9784,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.9980,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9820,0.0005,0.0135,0.0001</t>
+  </si>
+  <si>
+    <t>0.8624,0.0010,0.1419,0.0007</t>
+  </si>
+  <si>
+    <t>0.0018,0.0002,0.9963,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0235,0.0002,0.9878,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.3975,0.5379,0.0057,0.0009</t>
+  </si>
+  <si>
+    <t>0.9909,0.0028,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0008</t>
+  </si>
+  <si>
+    <t>0.0022,0.9912,0.0179,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0005,0.0030,0.0003</t>
+  </si>
+  <si>
+    <t>0.1224,0.8878,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.9976,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0066,0.1215,0.7888,0.0288</t>
+  </si>
+  <si>
+    <t>0.0029,0.0014,0.9761,0.0205</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9984,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0950,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.0045,0.9944,0.0007</t>
+  </si>
+  <si>
+    <t>0.0033,0.0041,0.0001,0.9965</t>
+  </si>
+  <si>
+    <t>0.0003,0.9987,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.1435,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0016,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0034,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0005,0.9956,0.0002</t>
+  </si>
+  <si>
+    <t>0.0081,0.0000,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9993,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0005,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0017,0.9999,0.0060</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.8451,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0005,0.9952,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.9978,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9932,0.0003,0.0059,0.0000</t>
+  </si>
+  <si>
+    <t>0.9483,0.0057,0.0270,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9995,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.9687,0.9954,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9705,0.9898,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9953,0.9661,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0851,0.9960</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0022,0.0004,0.0259,0.9873</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.9955,0.0383,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9516,0.9849,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9629,0.9433,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9823,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9831,0.9773,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0010,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0016,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0007,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.5645,0.0005,0.5037,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0065,0.9864,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.0074,0.9832,0.0055,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0756,0.9318,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.1135,0.0081,0.6395,0.0416</t>
+  </si>
+  <si>
+    <t>0.0071,0.0005,0.9863,0.0033</t>
+  </si>
+  <si>
+    <t>0.1476,0.0111,0.7859,0.0009</t>
+  </si>
+  <si>
+    <t>0.0045,0.0032,0.9896,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9920,0.9963,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9981,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.5392,0.2743,0.0429,0.0010</t>
+  </si>
+  <si>
+    <t>0.9647,0.0190,0.0045,0.0023</t>
+  </si>
+  <si>
+    <t>0.9975,0.0006,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9587,0.9321,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0407,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0013,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.3148,0.0026,0.6254,0.0075</t>
+  </si>
+  <si>
+    <t>0.0087,0.0001,0.9940,0.0002</t>
+  </si>
+  <si>
+    <t>0.9006,0.0054,0.0600,0.0003</t>
+  </si>
+  <si>
+    <t>0.0099,0.0000,0.0000,0.9985</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0004,0.9999</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.0038,0.9979</t>
+  </si>
+  <si>
+    <t>0.0000,0.9926,0.9950,0.0000</t>
+  </si>
+  <si>
+    <t>0.0465,0.9392,0.0036,0.0017</t>
+  </si>
+  <si>
+    <t>0.1468,0.8329,0.0041,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9748,0.0017,0.0007,0.0107</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0497,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.8741,0.0000,0.0147,0.0219</t>
+  </si>
+  <si>
+    <t>0.9960,0.0000,0.0003,0.0032</t>
+  </si>
+  <si>
+    <t>0.7623,0.1648,0.0067,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9938,0.0016,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.5741,0.0080,0.2623,0.0010</t>
+  </si>
+  <si>
+    <t>0.9952,0.0022,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9971,0.0008,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9182,0.0545,0.0062,0.0010</t>
+  </si>
+  <si>
+    <t>0.1837,0.7967,0.0095,0.0011</t>
+  </si>
+  <si>
+    <t>0.0571,0.0107,0.9636,0.0003</t>
+  </si>
+  <si>
+    <t>0.9848,0.0173,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9868,0.0093,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0138,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9873,0.0044,0.0044,0.0019</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0127,0.9943,0.0004</t>
+  </si>
+  <si>
+    <t>0.0603,0.0017,0.9513,0.0009</t>
+  </si>
+  <si>
+    <t>0.0031,0.0039,0.9933,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0028,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.0029,0.9910,0.0004</t>
+  </si>
+  <si>
+    <t>0.0118,0.0015,0.9870,0.0004</t>
+  </si>
+  <si>
+    <t>0.0253,0.0111,0.9164,0.0018</t>
+  </si>
+  <si>
+    <t>0.0581,0.0069,0.9096,0.0012</t>
+  </si>
+  <si>
+    <t>0.0020,0.0479,0.9654,0.0010</t>
+  </si>
+  <si>
+    <t>0.0049,0.0006,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.9747,0.0023,0.0052,0.0009</t>
+  </si>
+  <si>
+    <t>0.0075,0.0038,0.9833,0.0018</t>
+  </si>
+  <si>
+    <t>0.0094,0.9859,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.1624,0.8666,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.7841,0.3663,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0675,0.9489,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9739,0.0017,0.0116,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0002,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.9617,0.0002,0.0060,0.0049</t>
+  </si>
+  <si>
+    <t>0.2827,0.0037,0.7409,0.0005</t>
+  </si>
+  <si>
+    <t>0.0607,0.0002,0.9616,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0151,0.9946,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.0006,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.0006,0.9944,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.0170,0.9795,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0029,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9999,0.0006</t>
+  </si>
+  <si>
+    <t>0.0043,0.9616,0.0548,0.0020</t>
+  </si>
+  <si>
+    <t>0.3901,0.0001,0.4662,0.0116</t>
+  </si>
+  <si>
+    <t>0.0019,0.0001,0.9976,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0017,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.1145,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0052,0.0004,0.9919,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0115,0.9954,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.0006,0.9914,0.0019</t>
+  </si>
+  <si>
+    <t>0.9711,0.0004,0.0280,0.0001</t>
+  </si>
+  <si>
+    <t>0.8509,0.0005,0.1693,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9948,0.0045,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0016,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0036,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9990,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9534,0.0009,0.0432,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0007,0.9932,0.0009</t>
-  </si>
-  <si>
-    <t>0.3726,0.0026,0.6485,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0004,0.9960,0.0004</t>
-  </si>
-  <si>
-    <t>0.2642,0.0054,0.6994,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0061,0.9882,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.9978,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8676,0.0011,0.1113,0.0008</t>
-  </si>
-  <si>
-    <t>0.3721,0.0004,0.7594,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0004,0.9946,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.9431,0.0627,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9345,0.0049,0.0402,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0011</t>
-  </si>
-  <si>
-    <t>0.0002,0.9990,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.8433,0.1688,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.0021,0.9969,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0052,0.0361,0.9585,0.0044</t>
-  </si>
-  <si>
-    <t>0.0010,0.0012,0.9954,0.0016</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.9982,0.0006</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.9983,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.0040,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.0081,0.0014,0.9831,0.0023</t>
-  </si>
-  <si>
-    <t>0.0049,0.0007,0.0046,0.9863</t>
-  </si>
-  <si>
-    <t>0.0011,0.9975,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0190,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0013,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0810,0.9940,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0014,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0005,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0007,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0009</t>
-  </si>
-  <si>
-    <t>0.9981,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.8908,0.9915,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0022,0.9934,0.0019</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.9951,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9435,0.0004,0.0701,0.0002</t>
-  </si>
-  <si>
-    <t>0.7520,0.0017,0.2608,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9998,0.0020</t>
-  </si>
-  <si>
-    <t>0.0001,0.9534,0.9879,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9870,0.9855,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9739,0.6728,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0065,0.9993</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9977,0.0085,0.0032</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9763,0.9179,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.8624,0.9191,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9932,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9670,0.9941,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0001,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0268,0.0001,0.9831,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.9980,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.9916,0.0055,0.0007</t>
-  </si>
-  <si>
-    <t>0.0020,0.9949,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.6469,0.4003,0.0044,0.0004</t>
-  </si>
-  <si>
-    <t>0.9869,0.0039,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.2268,0.0009,0.8086,0.0006</t>
-  </si>
-  <si>
-    <t>0.2937,0.0022,0.6572,0.0023</t>
-  </si>
-  <si>
-    <t>0.0039,0.0044,0.9892,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0171,0.0003,0.9987</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9880,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9978,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.6022,0.3249,0.0040,0.0016</t>
-  </si>
-  <si>
-    <t>0.8932,0.0967,0.0064,0.0006</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9963,0.0008,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9979,0.0006,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9740,0.9674,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.7461,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0006,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0008,0.9964,0.0003</t>
-  </si>
-  <si>
-    <t>0.7947,0.0040,0.1417,0.0044</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.9472,0.0040,0.0197,0.0012</t>
-  </si>
-  <si>
-    <t>0.0108,0.0001,0.0000,0.9976</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0006,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.9558,0.9923,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.9952,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.1700,0.8156,0.0049,0.0005</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.6046,0.0001,0.0020,0.5263</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0189,0.9971,0.0004</t>
-  </si>
-  <si>
-    <t>0.9910,0.0001,0.0015,0.0037</t>
-  </si>
-  <si>
-    <t>0.9759,0.0000,0.0053,0.0038</t>
-  </si>
-  <si>
-    <t>0.8080,0.1848,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9934,0.0007,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.4604,0.4105,0.0060,0.0005</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0013,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0002,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9884,0.0086,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9268,0.0381,0.0129,0.0014</t>
-  </si>
-  <si>
-    <t>0.0371,0.9637,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.0054,0.0756,0.9932,0.0006</t>
-  </si>
-  <si>
-    <t>0.9856,0.0158,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9773,0.0175,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0075,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9780,0.0103,0.0065,0.0024</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.0102,0.9925,0.0009</t>
-  </si>
-  <si>
-    <t>0.0007,0.0012,0.9989,0.0005</t>
-  </si>
-  <si>
-    <t>0.0102,0.0059,0.9841,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6512,0.0018,0.2978,0.0026</t>
-  </si>
-  <si>
-    <t>0.0067,0.0003,0.9953,0.0001</t>
-  </si>
-  <si>
-    <t>0.1297,0.0084,0.7654,0.0019</t>
-  </si>
-  <si>
-    <t>0.2770,0.0096,0.6034,0.0004</t>
-  </si>
-  <si>
-    <t>0.0224,0.2772,0.6962,0.0003</t>
-  </si>
-  <si>
-    <t>0.3236,0.0046,0.6851,0.0000</t>
-  </si>
-  <si>
-    <t>0.8022,0.0014,0.0688,0.0061</t>
-  </si>
-  <si>
-    <t>0.0771,0.0010,0.9333,0.0007</t>
-  </si>
-  <si>
-    <t>0.4381,0.6706,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9991,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0666,0.9414,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.3314,0.7827,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.3434,0.7175,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9648,0.0090,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.9790,0.0009,0.0155,0.0000</t>
-  </si>
-  <si>
-    <t>0.9418,0.0003,0.0455,0.0008</t>
-  </si>
-  <si>
-    <t>0.7982,0.0009,0.2825,0.0001</t>
-  </si>
-  <si>
-    <t>0.8171,0.0007,0.2280,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0010,0.9967,0.0022</t>
-  </si>
-  <si>
-    <t>0.0055,0.0007,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.0006,0.9915,0.0012</t>
-  </si>
-  <si>
-    <t>0.0021,0.0956,0.9590,0.0006</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0013,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9803,0.0291,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0015,0.9996,0.0008</t>
-  </si>
-  <si>
-    <t>0.0040,0.0483,0.9713,0.0017</t>
-  </si>
-  <si>
-    <t>0.9825,0.0003,0.0092,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.2740,0.9900,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9970,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0114,0.0008,0.9770,0.0051</t>
-  </si>
-  <si>
-    <t>0.9765,0.0022,0.0106,0.0001</t>
-  </si>
-  <si>
-    <t>0.9897,0.0002,0.0064,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0020,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0013,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0019,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0022,0.9914,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.1662,0.9494,0.0016</t>
-  </si>
-  <si>
-    <t>0.0029,0.0759,0.9425,0.0007</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.5985,0.0001,0.3109,0.0067</t>
-  </si>
-  <si>
-    <t>0.0051,0.0013,0.9925,0.0002</t>
-  </si>
-  <si>
-    <t>0.0049,0.0003,0.9887,0.0021</t>
-  </si>
-  <si>
-    <t>0.9943,0.0002,0.0003,0.0024</t>
-  </si>
-  <si>
-    <t>0.0025,0.0049,0.0000,0.9987</t>
-  </si>
-  <si>
-    <t>0.0322,0.0001,0.0000,0.9954</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0002,0.0003</t>
+    <t>0.0001,0.0007,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0739,0.9914,0.0007</t>
+  </si>
+  <si>
+    <t>0.0182,0.0084,0.9617,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.3465,0.0002,0.5182,0.0085</t>
+  </si>
+  <si>
+    <t>0.0036,0.0005,0.9948,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9974,0.0006</t>
+  </si>
+  <si>
+    <t>0.9920,0.0002,0.0005,0.0050</t>
+  </si>
+  <si>
+    <t>0.0002,0.0008,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0206,0.0003,0.0000,0.9962</t>
+  </si>
+  <si>
+    <t>0.9012,0.0030,0.0010,0.0571</t>
   </si>
 </sst>
 </file>
@@ -1866,7 +1860,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1880,7 +1874,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1894,7 +1888,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1908,7 +1902,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1922,7 +1916,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1936,7 +1930,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1950,7 +1944,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1964,7 +1958,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1992,7 +1986,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2006,7 +2000,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2020,7 +2014,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2034,7 +2028,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2048,7 +2042,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2062,7 +2056,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2076,7 +2070,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2087,10 +2081,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2104,7 +2098,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2118,7 +2112,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2132,7 +2126,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2146,7 +2140,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2160,7 +2154,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2174,7 +2168,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2185,10 +2179,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2202,7 +2196,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2216,7 +2210,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2230,7 +2224,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2244,7 +2238,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2258,7 +2252,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2269,10 +2263,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2286,7 +2280,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2300,7 +2294,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2314,7 +2308,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2328,7 +2322,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2342,7 +2336,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2353,10 +2347,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2370,7 +2364,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2384,7 +2378,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2398,7 +2392,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2412,7 +2406,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2426,7 +2420,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2440,7 +2434,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2454,7 +2448,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2468,7 +2462,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2482,7 +2476,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2496,7 +2490,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2510,7 +2504,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2524,7 +2518,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2636,7 +2630,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2650,7 +2644,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2664,7 +2658,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2678,7 +2672,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2692,7 +2686,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2706,7 +2700,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2720,7 +2714,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2734,7 +2728,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2748,7 +2742,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2762,7 +2756,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2776,7 +2770,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2790,7 +2784,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2804,7 +2798,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2818,7 +2812,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2832,7 +2826,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2846,7 +2840,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2860,7 +2854,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2874,7 +2868,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2888,7 +2882,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2902,7 +2896,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2916,7 +2910,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2930,7 +2924,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2944,7 +2938,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2958,7 +2952,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2972,7 +2966,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2986,7 +2980,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3000,7 +2994,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3014,7 +3008,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3028,7 +3022,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3042,7 +3036,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3056,7 +3050,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3070,7 +3064,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3084,7 +3078,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3098,7 +3092,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3112,7 +3106,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3126,7 +3120,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3140,7 +3134,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3154,7 +3148,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3168,7 +3162,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3182,7 +3176,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3196,7 +3190,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3210,7 +3204,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3224,7 +3218,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3238,7 +3232,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3252,7 +3246,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3266,7 +3260,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3280,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3294,7 +3288,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3308,7 +3302,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3322,7 +3316,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3336,7 +3330,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>273</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3347,10 +3341,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3364,7 +3358,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3378,7 +3372,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3392,7 +3386,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3406,7 +3400,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3420,7 +3414,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3434,7 +3428,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3445,10 +3439,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3459,10 +3453,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3476,7 +3470,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3490,7 +3484,7 @@
         <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3504,7 +3498,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3518,7 +3512,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3532,7 +3526,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>281</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3546,7 +3540,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>373</v>
+        <v>281</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3560,7 +3554,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3574,7 +3568,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3588,7 +3582,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3602,7 +3596,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3616,7 +3610,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3630,7 +3624,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>273</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3644,7 +3638,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3658,7 +3652,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3672,7 +3666,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3686,7 +3680,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3700,7 +3694,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3714,7 +3708,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>384</v>
+        <v>273</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3728,7 +3722,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>385</v>
+        <v>274</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3742,7 +3736,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3753,10 +3747,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3770,7 +3764,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3784,7 +3778,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3798,7 +3792,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3809,10 +3803,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3826,7 +3820,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3840,7 +3834,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3854,7 +3848,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3868,7 +3862,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>394</v>
+        <v>338</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3882,7 +3876,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3896,7 +3890,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3910,7 +3904,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3924,7 +3918,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3938,7 +3932,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3952,7 +3946,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>398</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3966,7 +3960,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3980,7 +3974,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3991,10 +3985,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4008,7 +4002,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4022,7 +4016,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4036,7 +4030,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4050,7 +4044,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4064,7 +4058,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4078,7 +4072,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4092,7 +4086,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4106,7 +4100,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4120,7 +4114,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4134,7 +4128,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4148,7 +4142,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>349</v>
+        <v>404</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4162,7 +4156,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4176,7 +4170,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4190,7 +4184,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4204,7 +4198,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4218,7 +4212,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4232,7 +4226,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>354</v>
+        <v>408</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4246,7 +4240,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4260,7 +4254,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4274,7 +4268,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4288,7 +4282,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4302,7 +4296,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4316,7 +4310,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4330,7 +4324,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>381</v>
+        <v>414</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4344,7 +4338,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4358,7 +4352,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4372,7 +4366,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4386,7 +4380,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4400,7 +4394,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4414,7 +4408,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4428,7 +4422,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4442,7 +4436,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4456,7 +4450,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4470,7 +4464,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4484,7 +4478,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4495,10 +4489,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4512,7 +4506,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4526,7 +4520,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4540,7 +4534,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4554,7 +4548,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4568,7 +4562,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4582,7 +4576,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4596,7 +4590,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4610,7 +4604,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4624,7 +4618,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4638,7 +4632,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4649,10 +4643,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4666,7 +4660,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4680,7 +4674,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4694,7 +4688,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4708,7 +4702,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4719,10 +4713,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4733,10 +4727,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4750,7 +4744,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4764,7 +4758,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4778,7 +4772,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4792,7 +4786,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4806,7 +4800,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4820,7 +4814,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4834,7 +4828,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4848,7 +4842,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4862,7 +4856,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>458</v>
+        <v>275</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4876,7 +4870,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4890,7 +4884,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4904,7 +4898,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>461</v>
+        <v>377</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4918,7 +4912,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4932,7 +4926,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4943,10 +4937,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4957,10 +4951,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D223" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4974,7 +4968,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>313</v>
+        <v>457</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4988,7 +4982,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5002,7 +4996,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5016,7 +5010,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>328</v>
+        <v>460</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5030,7 +5024,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5044,7 +5038,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>328</v>
+        <v>462</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5058,7 +5052,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5072,7 +5066,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5086,7 +5080,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5100,7 +5094,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5114,7 +5108,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5128,7 +5122,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5142,7 +5136,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>323</v>
+        <v>469</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5156,7 +5150,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5170,7 +5164,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5184,7 +5178,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>268</v>
+        <v>377</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5198,7 +5192,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5212,7 +5206,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5226,7 +5220,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>272</v>
+        <v>474</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5240,7 +5234,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5254,7 +5248,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5268,7 +5262,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5282,7 +5276,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5296,7 +5290,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5307,10 +5301,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5324,7 +5318,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5338,7 +5332,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5352,7 +5346,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5366,7 +5360,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5380,7 +5374,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5394,7 +5388,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>394</v>
+        <v>338</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5408,7 +5402,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>394</v>
+        <v>338</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5422,7 +5416,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
